--- a/employee_surveys/006_remote_work_feedback_pulse_survey--employee_surveys.xlsx
+++ b/employee_surveys/006_remote_work_feedback_pulse_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What's your experience with remote work?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your experience.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>manager_name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Manager's Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide your manager's name.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>manager_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>employee_name</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Manager's Email</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide your manager's email address.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>satisfaction_score</t>
+          <t>manager_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>satisfaction_score</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Manager's Phone</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide your manager's phone number.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>productivity_score</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>productivity_score</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Your Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide your name.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>employee_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Your Email</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide your email address.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>employee_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Your Phone</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide your phone number.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>satisfaction_score</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Satisfaction Score (1-5)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please rate your satisfaction with remote work.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>productivity_score</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Productivity Score (1-5)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please rate your productivity with remote work.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>manager_comments</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>manager_comments</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Challenges Faced</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please list any challenges you faced with remote work.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>manager_satisfaction_score</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>manager_satisfaction_score</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Comments and Feedback</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide any comments or feedback.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,138 +812,162 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>manager_productivity_score</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>manager_productivity_score</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select the category that best describes your experience.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>manager_challenges</t>
+          <t>how_long_have</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>manager_challenges</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>How long have you worked remotely?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select the duration of your remote work experience.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>manager_comments</t>
+          <t>remote_duration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>manager_comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Duration of Remote Setup</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please select the duration of your remote work setup.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Other Category</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide any other category that best describes your experience.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>category_other</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>category_other</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Select Multiple</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please select multiple options that best describe your experience.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>date_experience</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>how_long_have</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Date of Experience</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide the date of your remote work experience.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,177 +979,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>end_screen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>End Screen</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Thank you for taking the time to share your feedback.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +1009,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,119 +1105,204 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>how_long_have_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>how_long_have_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>3-6_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>3-6 months</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>how_long_have_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>how_long_have_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>over_1_year</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>Over 1 year</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>remote_duration_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>1-2_days</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>1-2 days</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>remote_duration_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>2-4_days</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>2-4 days</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>remote_duration_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>4-5_days</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>4-5 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>remote_duration_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5-7_days</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5-7 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>remote_duration_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>more_than_7_days</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>More than 7 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
